--- a/data/trans_dic/P1802_2016_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1802_2016_2023-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,3; 25,92</t>
+          <t>16,23; 26,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,14; 36,75</t>
+          <t>22,79; 32,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,59; 30,95</t>
+          <t>20,82; 30,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,83; 44,24</t>
+          <t>33,41; 41,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,69; 26,52</t>
+          <t>19,34; 26,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,97; 38,63</t>
+          <t>29,78; 36,35</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,96</t>
+          <t>12,41; 18,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 13,84</t>
+          <t>8,35; 14,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 23,5</t>
+          <t>16,01; 23,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,33; 20,25</t>
+          <t>14,31; 20,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 20,04</t>
+          <t>15,13; 20,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,87; 16,13</t>
+          <t>12,01; 16,26</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,69</t>
+          <t>4,9; 10,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 27,08</t>
+          <t>18,16; 26,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,97</t>
+          <t>7,13; 14,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,79; 30,42</t>
+          <t>22,57; 30,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 11,15</t>
+          <t>6,56; 11,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 27,29</t>
+          <t>21,85; 27,51</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,94; 23,73</t>
+          <t>14,8; 23,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 21,95</t>
+          <t>10,31; 19,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,05; 27,19</t>
+          <t>17,83; 26,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 14,92</t>
+          <t>11,65; 17,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,6; 23,99</t>
+          <t>17,74; 23,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 16,6</t>
+          <t>11,85; 17,04</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 24,27</t>
+          <t>13,61; 24,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 17,7</t>
+          <t>8,07; 16,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,08; 23,82</t>
+          <t>13,64; 23,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,8</t>
+          <t>3,78; 7,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,0; 22,6</t>
+          <t>15,07; 22,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 11,77</t>
+          <t>6,66; 11,22</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 18,54</t>
+          <t>9,58; 17,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,78; 22,19</t>
+          <t>13,16; 20,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,08; 26,4</t>
+          <t>16,27; 25,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,42; 23,8</t>
+          <t>16,07; 23,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,04; 20,63</t>
+          <t>14,05; 20,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,96; 21,66</t>
+          <t>15,34; 21,08</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,98; 12,99</t>
+          <t>8,0; 13,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,25; 24,36</t>
+          <t>16,86; 23,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,75; 19,87</t>
+          <t>13,89; 19,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,85; 26,83</t>
+          <t>24,1; 30,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,59; 15,38</t>
+          <t>11,74; 15,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,4; 23,95</t>
+          <t>21,32; 25,74</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,18</t>
+          <t>12,15; 17,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 68,45</t>
+          <t>4,61; 8,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,44; 23,33</t>
+          <t>17,2; 22,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,9</t>
+          <t>5,96; 9,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,49; 19,31</t>
+          <t>15,16; 19,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,36; 50,47</t>
+          <t>5,62; 7,98</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,7</t>
+          <t>13,19; 15,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,49; 39,25</t>
+          <t>13,94; 16,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,59; 20,25</t>
+          <t>17,52; 20,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,19; 18,84</t>
+          <t>17,7; 19,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,77; 17,69</t>
+          <t>15,76; 17,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,11; 29,79</t>
+          <t>16,12; 17,77</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>94259</t>
+          <t>88891</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113900</t>
+          <t>119109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>208158</t>
+          <t>208000</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47892; 76149</t>
+          <t>47667; 76580</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78311; 114456</t>
+          <t>72670; 104559</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59445; 89351</t>
+          <t>60098; 89249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100883; 128147</t>
+          <t>105590; 131767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>114672; 154479</t>
+          <t>112621; 154525</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>186174; 232187</t>
+          <t>189062; 230801</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55027</t>
+          <t>58143</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88648</t>
+          <t>92602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>143675</t>
+          <t>150745</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63639; 95269</t>
+          <t>62353; 95181</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40058; 71769</t>
+          <t>44312; 76372</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85364; 122949</t>
+          <t>83754; 121816</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73418; 103758</t>
+          <t>77799; 109351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>154817; 205499</t>
+          <t>155166; 205865</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122376; 166285</t>
+          <t>129029; 174682</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70198</t>
+          <t>70411</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91548</t>
+          <t>93625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>161746</t>
+          <t>164036</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16731; 34070</t>
+          <t>15610; 33454</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57708; 85599</t>
+          <t>57384; 84660</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24021; 46992</t>
+          <t>23976; 47803</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79559; 106211</t>
+          <t>80441; 109032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44132; 73045</t>
+          <t>42989; 73863</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>140802; 181552</t>
+          <t>146890; 184952</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>51470</t>
+          <t>53471</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53820</t>
+          <t>60671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>105290</t>
+          <t>114142</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55254; 87807</t>
+          <t>54751; 86078</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37211; 68611</t>
+          <t>38458; 72593</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69899; 105286</t>
+          <t>69039; 102134</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32148; 70995</t>
+          <t>49164; 74253</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>133257; 181656</t>
+          <t>134349; 179050</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75368; 130849</t>
+          <t>94240; 135489</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34764</t>
+          <t>36748</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>28315; 51271</t>
+          <t>28752; 51399</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15727; 31642</t>
+          <t>16593; 34094</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30784; 52069</t>
+          <t>29814; 51896</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8299; 16278</t>
+          <t>8579; 17777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>64468; 97134</t>
+          <t>64765; 97641</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27045; 45606</t>
+          <t>28822; 48582</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46764</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51008</t>
+          <t>52030</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97772</t>
+          <t>97729</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25162; 48794</t>
+          <t>25218; 47151</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37151; 59823</t>
+          <t>35638; 56527</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43922; 72094</t>
+          <t>44425; 70066</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42213; 61169</t>
+          <t>42395; 62536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>75300; 110646</t>
+          <t>75335; 110504</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>84047; 114074</t>
+          <t>81961; 112648</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>128316</t>
+          <t>144544</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167011</t>
+          <t>207813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>295328</t>
+          <t>352357</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>52414; 85280</t>
+          <t>52526; 85405</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107456; 151715</t>
+          <t>121026; 168701</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>95065; 137352</t>
+          <t>95990; 138061</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83654; 227823</t>
+          <t>186039; 231832</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>156233; 207313</t>
+          <t>158183; 210775</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>182562; 352575</t>
+          <t>317610; 383582</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>287283</t>
+          <t>48714</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51165</t>
+          <t>61294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>338448</t>
+          <t>110009</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>94210; 133759</t>
+          <t>94567; 132443</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>52479; 635704</t>
+          <t>36801; 64639</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>144102; 192777</t>
+          <t>142087; 187639</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41418; 63819</t>
+          <t>49471; 75074</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>248619; 309957</t>
+          <t>243270; 307019</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>104712; 830764</t>
+          <t>91490; 129999</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>756412</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>628769</t>
+          <t>699733</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1385181</t>
+          <t>1233766</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>450601; 532950</t>
+          <t>447787; 530340</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>535648; 1357470</t>
+          <t>492282; 581716</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>623660; 717621</t>
+          <t>621069; 719257</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>519238; 689500</t>
+          <t>660448; 745858</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1094059; 1227221</t>
+          <t>1093456; 1223456</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1146383; 2120306</t>
+          <t>1170974; 1290464</t>
         </is>
       </c>
     </row>
